--- a/data/FTMO_100k_1.xlsx
+++ b/data/FTMO_100k_1.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="28">
   <si>
     <t>Mã số giao dịch</t>
   </si>
@@ -59,6 +59,21 @@
     <t>Thời lượng giao dịch tính bằng giây</t>
   </si>
   <si>
+    <t>146813712</t>
+  </si>
+  <si>
+    <t>2026-07-02 08:02:46</t>
+  </si>
+  <si>
+    <t>buy</t>
+  </si>
+  <si>
+    <t>BTCUSD</t>
+  </si>
+  <si>
+    <t>2026-07-03 17:09:44</t>
+  </si>
+  <si>
     <t>146160238</t>
   </si>
   <si>
@@ -68,9 +83,6 @@
     <t>sell</t>
   </si>
   <si>
-    <t>BTCUSD</t>
-  </si>
-  <si>
     <t>2026-07-01 04:39:24</t>
   </si>
   <si>
@@ -78,9 +90,6 @@
   </si>
   <si>
     <t>2026-06-29 13:00:43</t>
-  </si>
-  <si>
-    <t>buy</t>
   </si>
   <si>
     <t>USDJPY</t>
@@ -432,7 +441,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:O3"/>
+  <dimension ref="A1:O4"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="18.71" bestFit="true" customWidth="true" style="0"/>
@@ -448,7 +457,7 @@
     <col min="11" max="11" width="15.282" bestFit="true" customWidth="true" style="0"/>
     <col min="12" max="12" width="16.425" bestFit="true" customWidth="true" style="0"/>
     <col min="13" max="13" width="16.425" bestFit="true" customWidth="true" style="0"/>
-    <col min="14" max="14" width="15.282" bestFit="true" customWidth="true" style="0"/>
+    <col min="14" max="14" width="16.425" bestFit="true" customWidth="true" style="0"/>
     <col min="15" max="15" width="42.418" bestFit="true" customWidth="true" style="0"/>
   </cols>
   <sheetData>
@@ -510,40 +519,40 @@
         <v>17</v>
       </c>
       <c r="D2" s="2">
-        <v>0.66</v>
+        <v>0.46</v>
       </c>
       <c r="E2" t="s">
         <v>18</v>
       </c>
       <c r="F2" s="2">
-        <v>58999.31</v>
+        <v>60647.26</v>
       </c>
       <c r="G2" s="2">
-        <v>58914.82</v>
+        <v>58623.69</v>
       </c>
       <c r="H2" s="2">
-        <v>55880.16</v>
+        <v>65048.6</v>
       </c>
       <c r="I2" s="1" t="s">
         <v>19</v>
       </c>
       <c r="J2" s="2">
-        <v>58797.28</v>
+        <v>61968.08</v>
       </c>
       <c r="K2" s="2">
-        <v>-32.29</v>
+        <v>-23.54</v>
       </c>
       <c r="L2" s="2">
-        <v>-25.27</v>
+        <v>-18.33</v>
       </c>
       <c r="M2" s="2">
-        <v>133.34</v>
+        <v>607.58</v>
       </c>
       <c r="N2" s="2">
-        <v>202</v>
+        <v>1320.8</v>
       </c>
       <c r="O2" s="3">
-        <v>41514</v>
+        <v>119218</v>
       </c>
     </row>
     <row r="3" spans="1:15">
@@ -557,39 +566,86 @@
         <v>22</v>
       </c>
       <c r="D3" s="2">
+        <v>0.66</v>
+      </c>
+      <c r="E3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" s="2">
+        <v>58999.31</v>
+      </c>
+      <c r="G3" s="2">
+        <v>58914.82</v>
+      </c>
+      <c r="H3" s="2">
+        <v>55880.16</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="J3" s="2">
+        <v>58797.28</v>
+      </c>
+      <c r="K3" s="2">
+        <v>-32.29</v>
+      </c>
+      <c r="L3" s="2">
+        <v>-25.27</v>
+      </c>
+      <c r="M3" s="2">
+        <v>133.34</v>
+      </c>
+      <c r="N3" s="2">
+        <v>202</v>
+      </c>
+      <c r="O3" s="3">
+        <v>41514</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15">
+      <c r="A4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" s="2">
         <v>4.36</v>
       </c>
-      <c r="E3" t="s">
-        <v>23</v>
-      </c>
-      <c r="F3" s="2">
+      <c r="E4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F4" s="2">
         <v>161.902</v>
       </c>
-      <c r="G3" s="2">
+      <c r="G4" s="2">
         <v>161.925</v>
       </c>
-      <c r="H3" s="2">
+      <c r="H4" s="2">
         <v>162.648</v>
       </c>
-      <c r="I3" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="J3" s="2">
+      <c r="I4" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="J4" s="2">
         <v>162.61</v>
       </c>
-      <c r="K3" s="2">
+      <c r="K4" s="2">
         <v>10.1</v>
       </c>
-      <c r="L3" s="2">
+      <c r="L4" s="2">
         <v>-21.8</v>
       </c>
-      <c r="M3" s="2">
+      <c r="M4" s="2">
         <v>1898.33</v>
       </c>
-      <c r="N3" s="2">
+      <c r="N4" s="2">
         <v>70.8</v>
       </c>
-      <c r="O3" s="3">
+      <c r="O4" s="3">
         <v>106808</v>
       </c>
     </row>
